--- a/xlsx/cards-pages/cards.bankcode.xlsx
+++ b/xlsx/cards-pages/cards.bankcode.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25515" windowHeight="12015"/>
+    <workbookView windowWidth="25515" windowHeight="8010" tabRatio="563"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$AG$17</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="94">
   <si>
     <t>row_seq</t>
   </si>
@@ -134,13 +137,34 @@
     <t>中国</t>
   </si>
   <si>
+    <t>浙商银行</t>
+  </si>
+  <si>
+    <t>https://czbank.com/cn/images/favicon.ico,#FFFFFF</t>
+  </si>
+  <si>
+    <t>官网首页</t>
+  </si>
+  <si>
+    <t>https://czbank.com/</t>
+  </si>
+  <si>
+    <t>联行号查询</t>
+  </si>
+  <si>
+    <t>https://corbank.czbank.com/CORPORBANK/query_unionBank_index.jsp</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
     <t>中国工商银行</t>
   </si>
   <si>
-    <t>95588,</t>
-  </si>
-  <si>
-    <t>官网首页</t>
+    <t>客服热线：95588</t>
+  </si>
+  <si>
+    <t>https://www.icbc.com.cn/favicon.ico,#FFFFFF</t>
   </si>
   <si>
     <t>https://www.icbc.com.cn</t>
@@ -158,13 +182,13 @@
     <t>https://www.icbc.com.cn/column/1438058341489590354.html</t>
   </si>
   <si>
-    <t>True</t>
-  </si>
-  <si>
     <t>中国建设银行</t>
   </si>
   <si>
-    <t>95533,</t>
+    <t>客服热线：95533</t>
+  </si>
+  <si>
+    <t>https://ccb.com/chn/imageDir/siteIcon.ico,#FFFFFF</t>
   </si>
   <si>
     <t>https://ccb.com</t>
@@ -173,7 +197,10 @@
     <t>中国农业银行</t>
   </si>
   <si>
-    <t>95599,</t>
+    <t>客服热线：95599</t>
+  </si>
+  <si>
+    <t>https://www.abchina.com/favicon.ico,#FFFFFF</t>
   </si>
   <si>
     <t>https://www.abchina.com</t>
@@ -188,42 +215,84 @@
     <t>中国银行</t>
   </si>
   <si>
+    <t>客服热线：95666</t>
+  </si>
+  <si>
+    <t>https://www.boc.cn/favicon.ico,#FFFFFF</t>
+  </si>
+  <si>
     <t>https://www.boc.cn</t>
   </si>
   <si>
     <t>交通银行</t>
   </si>
   <si>
+    <t>客服热线：95559</t>
+  </si>
+  <si>
+    <t>https://www.95559.com.cn/favicon.ico,#FFFFFF</t>
+  </si>
+  <si>
     <t>https://www.95559.com.cn</t>
   </si>
   <si>
     <t>浦发银行</t>
   </si>
   <si>
+    <t>客服热线：95528</t>
+  </si>
+  <si>
+    <t>https://www.spdb.com.cn/images/favicon.ico,#FFFFFF</t>
+  </si>
+  <si>
     <t>https://www.95528.cn/</t>
   </si>
   <si>
     <t>招商银行</t>
   </si>
   <si>
+    <t>客服热线：95555</t>
+  </si>
+  <si>
+    <t>https://cmbchina.com/cmb.ico,#FFFFFF</t>
+  </si>
+  <si>
     <t>https://cmbchina.com/</t>
   </si>
   <si>
     <t>中国民生银行</t>
   </si>
   <si>
+    <t>客服热线：95568</t>
+  </si>
+  <si>
+    <t>https://www.cmbc.com.cn/cmbc_new/imageDir/siteIcon.ico,#FFFFFF</t>
+  </si>
+  <si>
     <t>https://www.cmbc.com.cn/</t>
   </si>
   <si>
     <t>兴业银行</t>
   </si>
   <si>
+    <t>客服热线：95561</t>
+  </si>
+  <si>
+    <t>https://www.cib.com.cn/favicon.ico,#FFFFFF</t>
+  </si>
+  <si>
     <t>https://www.cib.com.cn/</t>
   </si>
   <si>
     <t>平安银行</t>
   </si>
   <si>
+    <t>客服热线：95511</t>
+  </si>
+  <si>
+    <t>https://bank.pingan.com/favicon.ico,#FFFFFF</t>
+  </si>
+  <si>
     <t>https://bank.pingan.com/</t>
   </si>
   <si>
@@ -233,10 +302,10 @@
     <t>中国邮政储蓄银行</t>
   </si>
   <si>
-    <t>https://www.psbc.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>95580,</t>
+    <t>客服热线：95580</t>
+  </si>
+  <si>
+    <t>https://www.psbc.com/favicon.ico,#FFFFFF</t>
   </si>
   <si>
     <t>https://www.psbc.com</t>
@@ -255,7 +324,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,13 +346,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -718,19 +780,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -739,7 +801,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -748,125 +813,124 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1216,16 +1280,19 @@
   <dimension ref="A1:AG17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="2.75" customWidth="1"/>
+    <col min="4" max="4" width="5.625" customWidth="1"/>
+    <col min="5" max="5" width="5.375" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="38.75" customWidth="1"/>
+    <col min="9" max="9" width="21.875" customWidth="1"/>
     <col min="10" max="10" width="4.875" customWidth="1"/>
     <col min="11" max="11" width="3.75" customWidth="1"/>
     <col min="12" max="12" width="9.25" customWidth="1"/>
     <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="9.125" customWidth="1"/>
+    <col min="14" max="14" width="12.875" customWidth="1"/>
     <col min="16" max="31" width="1.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1346,14 +1413,13 @@
       <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="G2"/>
-      <c r="I2" t="s">
+      <c r="H2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N2" t="s">
@@ -1362,14 +1428,8 @@
       <c r="O2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P2" t="s">
+      <c r="AF2" t="s">
         <v>41</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -1386,20 +1446,34 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="G3"/>
-      <c r="I3" t="s">
-        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" t="s">
         <v>46</v>
       </c>
+      <c r="O3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="AF3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -1416,25 +1490,22 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="L4" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>51</v>
+      <c r="M4" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="AF4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1451,19 +1522,28 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5">
-        <v>95666</v>
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="L5" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>53</v>
+      <c r="M5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="AF5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1480,19 +1560,22 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6">
-        <v>95559</v>
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="L6" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>55</v>
+      <c r="M6" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="AF6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1509,19 +1592,22 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7">
-        <v>95528</v>
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="L7" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>57</v>
+      <c r="M7" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="AF7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -1538,19 +1624,22 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8">
-        <v>95555</v>
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="L8" t="s">
         <v>37</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>59</v>
+      <c r="M8" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="AF8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -1567,19 +1656,22 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9">
-        <v>95568</v>
+        <v>72</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>37</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>61</v>
+      <c r="M9" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="AF9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -1596,20 +1688,22 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10">
-        <v>95561</v>
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="L10" t="s">
         <v>37</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10"/>
+      <c r="M10" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AF10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -1626,25 +1720,22 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11">
-        <v>95511</v>
+        <v>80</v>
+      </c>
+      <c r="G11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="L11" t="s">
         <v>37</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N11" t="s">
-        <v>50</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>66</v>
+      <c r="M11" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="AF11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -1661,51 +1752,109 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>84</v>
+      </c>
+      <c r="G12" t="s">
+        <v>85</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="L12" t="s">
         <v>37</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>70</v>
+      <c r="M12" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="N12" t="s">
-        <v>50</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="AF12" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" t="s">
+        <v>58</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="15:15">
-      <c r="O17" s="1"/>
+      <c r="O17" s="3"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AG17" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:AG17">
+      <sortCondition ref="A1"/>
+    </sortState>
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H12" r:id="rId1" display="https://www.psbc.com/favicon.ico"/>
-    <hyperlink ref="M12" r:id="rId2" display="https://www.psbc.com" tooltip="https://www.psbc.com"/>
-    <hyperlink ref="O12" r:id="rId3" display="https://www.psbc.com/cn/common/sitemap/"/>
-    <hyperlink ref="O4" r:id="rId4" display="https://www.abchina.com.cn/cn/PublicPlate/websitemap_new/"/>
-    <hyperlink ref="M4" r:id="rId5" display="https://www.abchina.com" tooltip="https://www.abchina.com"/>
-    <hyperlink ref="Q2" r:id="rId6" display="https://www.icbc.com.cn/column/1438058341489590354.html"/>
-    <hyperlink ref="O2" r:id="rId7" display="https://www.icbc.com.cn/column/1438058326469787769.html"/>
-    <hyperlink ref="M3" r:id="rId8" display="https://ccb.com"/>
-    <hyperlink ref="M5" r:id="rId9" display="https://www.boc.cn" tooltip="https://www.boc.cn"/>
-    <hyperlink ref="M6" r:id="rId10" display="https://www.95559.com.cn" tooltip="https://www.95559.com.cn"/>
-    <hyperlink ref="M7" r:id="rId11" display="https://www.95528.cn/"/>
-    <hyperlink ref="M8" r:id="rId12" display="https://cmbchina.com/"/>
-    <hyperlink ref="M9" r:id="rId13" display="https://www.cmbc.com.cn/"/>
-    <hyperlink ref="M10" r:id="rId14" display="https://www.cib.com.cn/"/>
-    <hyperlink ref="M11" r:id="rId15" display="https://bank.pingan.com/"/>
-    <hyperlink ref="O11" r:id="rId16" display="https://bank.pingan.com/sitemap.shtml"/>
+    <hyperlink ref="M13" r:id="rId1" display="https://www.psbc.com" tooltip="https://www.psbc.com"/>
+    <hyperlink ref="O13" r:id="rId2" display="https://www.psbc.com/cn/common/sitemap/"/>
+    <hyperlink ref="O5" r:id="rId3" display="https://www.abchina.com.cn/cn/PublicPlate/websitemap_new/"/>
+    <hyperlink ref="M5" r:id="rId4" display="https://www.abchina.com" tooltip="https://www.abchina.com"/>
+    <hyperlink ref="Q3" r:id="rId5" display="https://www.icbc.com.cn/column/1438058341489590354.html"/>
+    <hyperlink ref="O3" r:id="rId6" display="https://www.icbc.com.cn/column/1438058326469787769.html"/>
+    <hyperlink ref="M4" r:id="rId7" display="https://ccb.com"/>
+    <hyperlink ref="M6" r:id="rId8" display="https://www.boc.cn" tooltip="https://www.boc.cn"/>
+    <hyperlink ref="M7" r:id="rId9" display="https://www.95559.com.cn" tooltip="https://www.95559.com.cn"/>
+    <hyperlink ref="M8" r:id="rId10" display="https://www.95528.cn/"/>
+    <hyperlink ref="M9" r:id="rId11" display="https://cmbchina.com/"/>
+    <hyperlink ref="M10" r:id="rId12" display="https://www.cmbc.com.cn/"/>
+    <hyperlink ref="M11" r:id="rId13" display="https://www.cib.com.cn/"/>
+    <hyperlink ref="M12" r:id="rId14" display="https://bank.pingan.com/"/>
+    <hyperlink ref="O12" r:id="rId15" display="https://bank.pingan.com/sitemap.shtml"/>
+    <hyperlink ref="H2" r:id="rId16" display="https://czbank.com/cn/images/favicon.ico,#FFFFFF" tooltip="https://czbank.com/cn/images/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="M2" r:id="rId17" display="https://czbank.com/"/>
+    <hyperlink ref="H13" r:id="rId18" display="https://www.psbc.com/favicon.ico,#FFFFFF" tooltip="https://www.psbc.com/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="O2" r:id="rId19" display="https://corbank.czbank.com/CORPORBANK/query_unionBank_index.jsp"/>
+    <hyperlink ref="H7" r:id="rId20" display="https://www.95559.com.cn/favicon.ico,#FFFFFF" tooltip="https://www.95559.com.cn/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="M3" r:id="rId21" display="https://www.icbc.com.cn"/>
+    <hyperlink ref="H3" r:id="rId22" display="https://www.icbc.com.cn/favicon.ico,#FFFFFF" tooltip="https://www.icbc.com.cn/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="H4" r:id="rId23" display="https://ccb.com/chn/imageDir/siteIcon.ico,#FFFFFF" tooltip="https://ccb.com/chn/imageDir/siteIcon.ico,#FFFFFF"/>
+    <hyperlink ref="H5" r:id="rId24" display="https://www.abchina.com/favicon.ico,#FFFFFF" tooltip="https://www.abchina.com/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="H6" r:id="rId25" display="https://www.boc.cn/favicon.ico,#FFFFFF" tooltip="https://www.boc.cn/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="H8" r:id="rId26" display="https://www.spdb.com.cn/images/favicon.ico,#FFFFFF" tooltip="https://www.spdb.com.cn/images/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="H9" r:id="rId27" display="https://cmbchina.com/cmb.ico,#FFFFFF" tooltip="https://cmbchina.com/cmb.ico,#FFFFFF"/>
+    <hyperlink ref="H10" r:id="rId28" display="https://www.cmbc.com.cn/cmbc_new/imageDir/siteIcon.ico,#FFFFFF" tooltip="https://www.cmbc.com.cn/cmbc_new/imageDir/siteIcon.ico,#FFFFFF"/>
+    <hyperlink ref="H11" r:id="rId29" display="https://www.cib.com.cn/favicon.ico,#FFFFFF" tooltip="https://www.cib.com.cn/favicon.ico,#FFFFFF"/>
+    <hyperlink ref="H12" r:id="rId30" display="https://bank.pingan.com/favicon.ico,#FFFFFF" tooltip="https://bank.pingan.com/favicon.ico,#FFFFFF"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
